--- a/jpcore-r4b/feature/merge-v1.2.0/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4b/feature/merge-v1.2.0/StructureDefinition-jp-procedure.xlsx
@@ -578,7 +578,7 @@
     <t>このプロシジャーが構成要素やステップとなるより大きな医療行為</t>
   </si>
   <si>
-    <t>【JP Core仕様】https://www.hl7.org/fhir/R4/procedure.htmlを参照</t>
+    <t>【JP Core仕様】https://www.hl7.org/fhir/R4B/procedure.htmlを参照</t>
   </si>
   <si>
     <t>MedicationAdministrationリソースにはProcedureへのpartOf参照があるが、これは循環参照ではない。たとえば、麻酔MedicationAdministrationは外科的処置の一部である（MedicationAdministration.partOf = Procedure）。  
@@ -1589,7 +1589,7 @@
     <t>Kind of change to device</t>
   </si>
   <si>
-    <t>Procedure中にデバイスに起こった変化の種類。【JP Core仕様】https://www.hl7.org/fhir/R4/procedure.htmlを参照</t>
+    <t>Procedure中にデバイスに起こった変化の種類。【JP Core仕様】https://www.hl7.org/fhir/R4B/procedure.htmlを参照</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureDeviceAction_VS</t>
@@ -1608,7 +1608,7 @@
     <t>Device that was changed</t>
   </si>
   <si>
-    <t>Procedure中に操作（変更）されたデバイス。【JP Core仕様】https://www.hl7.org/fhir/R4/procedure.htmlを参照</t>
+    <t>Procedure中に操作（変更）されたデバイス。【JP Core仕様】https://www.hl7.org/fhir/R4B/procedure.htmlを参照</t>
   </si>
   <si>
     <t>.participation[typeCode=DEV].role[classCode=SDLOC]</t>
